--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>136065801</v>
       </c>
       <c r="B8" t="n">
-        <v>111651</v>
+        <v>111658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136065749</v>
       </c>
       <c r="B9" t="n">
-        <v>99317</v>
+        <v>99320</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136065750</v>
       </c>
       <c r="B10" t="n">
-        <v>99320</v>
+        <v>99323</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136065751</v>
       </c>
       <c r="B11" t="n">
-        <v>99327</v>
+        <v>99330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136065748</v>
       </c>
       <c r="B12" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136065767</v>
       </c>
       <c r="B13" t="n">
-        <v>108359</v>
+        <v>108362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136065770</v>
       </c>
       <c r="B14" t="n">
-        <v>108359</v>
+        <v>108362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136065781</v>
       </c>
       <c r="B15" t="n">
-        <v>108359</v>
+        <v>108362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136065802</v>
       </c>
       <c r="B16" t="n">
-        <v>108359</v>
+        <v>108362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>136065786</v>
       </c>
       <c r="B17" t="n">
-        <v>104877</v>
+        <v>104880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136065791</v>
       </c>
       <c r="B18" t="n">
-        <v>104877</v>
+        <v>104880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136065796</v>
       </c>
       <c r="B19" t="n">
-        <v>104877</v>
+        <v>104880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136065763</v>
       </c>
       <c r="B20" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136065769</v>
       </c>
       <c r="B21" t="n">
-        <v>107053</v>
+        <v>107056</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136065753</v>
       </c>
       <c r="B22" t="n">
-        <v>106379</v>
+        <v>106382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136065785</v>
       </c>
       <c r="B23" t="n">
-        <v>107760</v>
+        <v>107763</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136065790</v>
       </c>
       <c r="B24" t="n">
-        <v>107760</v>
+        <v>107763</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>136065783</v>
       </c>
       <c r="B25" t="n">
-        <v>107301</v>
+        <v>107304</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>136065789</v>
       </c>
       <c r="B26" t="n">
-        <v>107301</v>
+        <v>107304</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>136065754</v>
       </c>
       <c r="B27" t="n">
-        <v>100396</v>
+        <v>100399</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>136065761</v>
       </c>
       <c r="B28" t="n">
-        <v>99148</v>
+        <v>99151</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>136065801</v>
       </c>
       <c r="B8" t="n">
-        <v>111658</v>
+        <v>111659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136065749</v>
       </c>
       <c r="B9" t="n">
-        <v>99320</v>
+        <v>99321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>136065750</v>
       </c>
       <c r="B10" t="n">
-        <v>99323</v>
+        <v>99324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>136065751</v>
       </c>
       <c r="B11" t="n">
-        <v>99330</v>
+        <v>99331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136065748</v>
       </c>
       <c r="B12" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>136065767</v>
       </c>
       <c r="B13" t="n">
-        <v>108362</v>
+        <v>108363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>136065770</v>
       </c>
       <c r="B14" t="n">
-        <v>108362</v>
+        <v>108363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>136065781</v>
       </c>
       <c r="B15" t="n">
-        <v>108362</v>
+        <v>108363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136065802</v>
       </c>
       <c r="B16" t="n">
-        <v>108362</v>
+        <v>108363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>136065786</v>
       </c>
       <c r="B17" t="n">
-        <v>104880</v>
+        <v>104881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>136065791</v>
       </c>
       <c r="B18" t="n">
-        <v>104880</v>
+        <v>104881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136065796</v>
       </c>
       <c r="B19" t="n">
-        <v>104880</v>
+        <v>104881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136065763</v>
       </c>
       <c r="B20" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>136065769</v>
       </c>
       <c r="B21" t="n">
-        <v>107056</v>
+        <v>107057</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>136065753</v>
       </c>
       <c r="B22" t="n">
-        <v>106382</v>
+        <v>106383</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>136065785</v>
       </c>
       <c r="B23" t="n">
-        <v>107763</v>
+        <v>107764</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136065790</v>
       </c>
       <c r="B24" t="n">
-        <v>107763</v>
+        <v>107764</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>136065783</v>
       </c>
       <c r="B25" t="n">
-        <v>107304</v>
+        <v>107305</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>136065789</v>
       </c>
       <c r="B26" t="n">
-        <v>107304</v>
+        <v>107305</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>136065754</v>
       </c>
       <c r="B27" t="n">
-        <v>100399</v>
+        <v>100400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>136065761</v>
       </c>
       <c r="B28" t="n">
-        <v>99151</v>
+        <v>99152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136065647</v>
+        <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>100581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>721143</v>
+        <v>721167</v>
       </c>
       <c r="R2" t="n">
-        <v>6379301</v>
+        <v>6379291</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,17 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Granlågor med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,16 +790,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065647</t>
+          <t>https://artportalen.se/Sighting/136771239</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136065648</v>
+        <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>58003</v>
+        <v>100581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,39 +807,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>174</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>721106</v>
+        <v>721166</v>
       </c>
       <c r="R3" t="n">
-        <v>6379267</v>
+        <v>6379273</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,17 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,16 +906,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065648</t>
+          <t>https://artportalen.se/Sighting/136771244</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136065649</v>
+        <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>58003</v>
+        <v>100581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,39 +923,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>174</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721105</v>
+        <v>721170</v>
       </c>
       <c r="R4" t="n">
-        <v>6379264</v>
+        <v>6379259</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,17 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +1005,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1025,16 +1022,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065649</t>
+          <t>https://artportalen.se/Sighting/136771247</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136065650</v>
+        <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>58003</v>
+        <v>100581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +1039,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>174</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721083</v>
+        <v>721177</v>
       </c>
       <c r="R5" t="n">
-        <v>6379258</v>
+        <v>6379254</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,17 +1102,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1142,13 +1138,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065650</t>
+          <t>https://artportalen.se/Sighting/136771251</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136065651</v>
+        <v>136065647</v>
       </c>
       <c r="B6" t="n">
         <v>58003</v>
@@ -1188,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721066</v>
+        <v>721143</v>
       </c>
       <c r="R6" t="n">
-        <v>6379261</v>
+        <v>6379301</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,7 +1224,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>Granlågor med gott om insektshål; äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,13 +1255,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065651</t>
+          <t>https://artportalen.se/Sighting/136065647</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136065652</v>
+        <v>136065648</v>
       </c>
       <c r="B7" t="n">
         <v>58003</v>
@@ -1305,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721058</v>
+        <v>721106</v>
       </c>
       <c r="R7" t="n">
-        <v>6379242</v>
+        <v>6379267</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1376,51 +1372,56 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065652</t>
+          <t>https://artportalen.se/Sighting/136065648</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136065801</v>
+        <v>136065649</v>
       </c>
       <c r="B8" t="n">
-        <v>111659</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219719</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Säfferot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Seseli libanotis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) W. D. J. Koch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721038</v>
+        <v>721105</v>
       </c>
       <c r="R8" t="n">
-        <v>6379233</v>
+        <v>6379264</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,6 +1456,11 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1466,7 +1472,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1483,16 +1489,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065801</t>
+          <t>https://artportalen.se/Sighting/136065649</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136065749</v>
+        <v>136065650</v>
       </c>
       <c r="B9" t="n">
-        <v>99321</v>
+        <v>58003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,37 +1506,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721106</v>
+        <v>721083</v>
       </c>
       <c r="R9" t="n">
-        <v>6379184</v>
+        <v>6379258</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,6 +1573,11 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1573,7 +1589,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1590,16 +1606,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065749</t>
+          <t>https://artportalen.se/Sighting/136065650</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136065750</v>
+        <v>136065651</v>
       </c>
       <c r="B10" t="n">
-        <v>99324</v>
+        <v>58003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,37 +1623,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721106</v>
+        <v>721066</v>
       </c>
       <c r="R10" t="n">
-        <v>6379184</v>
+        <v>6379261</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1669,6 +1690,11 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1680,7 +1706,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1697,16 +1723,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065750</t>
+          <t>https://artportalen.se/Sighting/136065651</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136065751</v>
+        <v>136065652</v>
       </c>
       <c r="B11" t="n">
-        <v>99331</v>
+        <v>58003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,37 +1740,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219799</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721106</v>
+        <v>721058</v>
       </c>
       <c r="R11" t="n">
-        <v>6379184</v>
+        <v>6379242</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,6 +1807,11 @@
           <t>2026-08-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1787,7 +1823,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1804,16 +1840,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065751</t>
+          <t>https://artportalen.se/Sighting/136065652</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136065748</v>
+        <v>136774891</v>
       </c>
       <c r="B12" t="n">
-        <v>99348</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,37 +1857,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219811</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721106</v>
+        <v>721203</v>
       </c>
       <c r="R12" t="n">
-        <v>6379184</v>
+        <v>6379231</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,12 +1916,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Död gran något S koordinat med insektshål och med äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,7 +1940,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1911,60 +1957,56 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065748</t>
+          <t>https://artportalen.se/Sighting/136774891</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136065767</v>
+        <v>136774892</v>
       </c>
       <c r="B13" t="n">
-        <v>108363</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721104</v>
+        <v>721257</v>
       </c>
       <c r="R13" t="n">
-        <v>6379290</v>
+        <v>6379277</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1991,17 +2033,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Tätare skog med gran.</t>
+          <t>Grov, död stånde tall, insektsangripen, med äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,7 +2057,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2032,63 +2074,59 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065767</t>
+          <t>https://artportalen.se/Sighting/136774892</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136065770</v>
+        <v>136774893</v>
       </c>
       <c r="B14" t="n">
-        <v>108363</v>
+        <v>58005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721107</v>
+        <v>721264</v>
       </c>
       <c r="R14" t="n">
-        <v>6379284</v>
+        <v>6379267</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2112,12 +2150,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gran, död,  låga med gott om insektshål med äldre födosök av spillkråka. Grov, död stånde tall, insektsangripen, med äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,7 +2174,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2148,54 +2191,59 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065770</t>
+          <t>https://artportalen.se/Sighting/136774893</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136065781</v>
+        <v>136774894</v>
       </c>
       <c r="B15" t="n">
-        <v>108363</v>
+        <v>58005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721066</v>
+        <v>721290</v>
       </c>
       <c r="R15" t="n">
-        <v>6379261</v>
+        <v>6379243</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,12 +2267,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Granar, 4 st. döda,  med gott om insektshål med äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,7 +2291,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2255,51 +2308,56 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065781</t>
+          <t>https://artportalen.se/Sighting/136774894</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136065802</v>
+        <v>136774895</v>
       </c>
       <c r="B16" t="n">
-        <v>108363</v>
+        <v>58005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721038</v>
+        <v>721296</v>
       </c>
       <c r="R16" t="n">
-        <v>6379233</v>
+        <v>6379235</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2326,12 +2384,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Granlåga med gott om insektshål med äldre födosök av spillkråka. Dessutom en död stående.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,7 +2408,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2362,51 +2425,56 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065802</t>
+          <t>https://artportalen.se/Sighting/136774895</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136065786</v>
+        <v>136774896</v>
       </c>
       <c r="B17" t="n">
-        <v>104881</v>
+        <v>58005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721065</v>
+        <v>721314</v>
       </c>
       <c r="R17" t="n">
-        <v>6379250</v>
+        <v>6379233</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2433,12 +2501,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Granlågor 2 med insektshål, varav båda har födosökts av spillkråka.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,7 +2525,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Tallskog på äldre strandvall med silikatsten.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2469,51 +2542,56 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065786</t>
+          <t>https://artportalen.se/Sighting/136774896</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136065791</v>
+        <v>136774897</v>
       </c>
       <c r="B18" t="n">
-        <v>104881</v>
+        <v>58005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721062</v>
+        <v>721357</v>
       </c>
       <c r="R18" t="n">
-        <v>6379242</v>
+        <v>6379269</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,12 +2618,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Grov, död tall, insektsangripen, liggande i luften med stödgrenar mot mark. Med äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,7 +2642,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2576,51 +2659,56 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065791</t>
+          <t>https://artportalen.se/Sighting/136774897</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136065796</v>
+        <v>136774898</v>
       </c>
       <c r="B19" t="n">
-        <v>104881</v>
+        <v>58005</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721053</v>
+        <v>721305</v>
       </c>
       <c r="R19" t="n">
-        <v>6379240</v>
+        <v>6379306</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,12 +2735,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosök i 2 döda granar med insektsangrepp.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,7 +2759,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2683,51 +2776,56 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065796</t>
+          <t>https://artportalen.se/Sighting/136774898</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136065763</v>
+        <v>136774899</v>
       </c>
       <c r="B20" t="n">
-        <v>110326</v>
+        <v>58005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721133</v>
+        <v>721315</v>
       </c>
       <c r="R20" t="n">
-        <v>6379293</v>
+        <v>6379289</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2754,12 +2852,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosök (äldre) i grov, död tall med insektsangrepp.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,7 +2876,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2790,33 +2893,33 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065763</t>
+          <t>https://artportalen.se/Sighting/136774899</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136065769</v>
+        <v>136771236</v>
       </c>
       <c r="B21" t="n">
-        <v>107057</v>
+        <v>111649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>219711</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2824,17 +2927,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721107</v>
+        <v>721167</v>
       </c>
       <c r="R21" t="n">
-        <v>6379284</v>
+        <v>6379301</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2861,12 +2973,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2880,7 +2992,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2897,16 +3009,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065769</t>
+          <t>https://artportalen.se/Sighting/136771236</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136065753</v>
+        <v>136065801</v>
       </c>
       <c r="B22" t="n">
-        <v>106383</v>
+        <v>111659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,21 +3026,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221137</v>
+        <v>219719</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Säfferot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Seseli libanotis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) W. D. J. Koch</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2938,13 +3050,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721106</v>
+        <v>721038</v>
       </c>
       <c r="R22" t="n">
-        <v>6379184</v>
+        <v>6379233</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2987,7 +3099,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3004,38 +3116,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065753</t>
+          <t>https://artportalen.se/Sighting/136065801</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136065785</v>
+        <v>136065749</v>
       </c>
       <c r="B23" t="n">
-        <v>107764</v>
+        <v>99321</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3045,13 +3157,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721065</v>
+        <v>721106</v>
       </c>
       <c r="R23" t="n">
-        <v>6379250</v>
+        <v>6379184</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3094,7 +3206,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3111,38 +3223,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065785</t>
+          <t>https://artportalen.se/Sighting/136065749</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136065790</v>
+        <v>136065750</v>
       </c>
       <c r="B24" t="n">
-        <v>107764</v>
+        <v>99324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3152,13 +3264,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721062</v>
+        <v>721106</v>
       </c>
       <c r="R24" t="n">
-        <v>6379242</v>
+        <v>6379184</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3201,7 +3313,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3218,51 +3330,60 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065790</t>
+          <t>https://artportalen.se/Sighting/136065750</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136065783</v>
+        <v>136771218</v>
       </c>
       <c r="B25" t="n">
-        <v>107305</v>
+        <v>99329</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721065</v>
+        <v>721212</v>
       </c>
       <c r="R25" t="n">
-        <v>6379250</v>
+        <v>6379283</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3289,12 +3410,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,7 +3429,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3325,51 +3446,60 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065783</t>
+          <t>https://artportalen.se/Sighting/136771218</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136065789</v>
+        <v>136771219</v>
       </c>
       <c r="B26" t="n">
-        <v>107305</v>
+        <v>99329</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221903</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721062</v>
+        <v>721206</v>
       </c>
       <c r="R26" t="n">
-        <v>6379242</v>
+        <v>6379274</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3396,12 +3526,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,7 +3545,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3432,16 +3562,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065789</t>
+          <t>https://artportalen.se/Sighting/136771219</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136065754</v>
+        <v>136771250</v>
       </c>
       <c r="B27" t="n">
-        <v>100400</v>
+        <v>99329</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3449,37 +3579,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222662</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721106</v>
+        <v>721177</v>
       </c>
       <c r="R27" t="n">
-        <v>6379184</v>
+        <v>6379254</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3503,12 +3642,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,7 +3661,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3539,16 +3678,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065754</t>
+          <t>https://artportalen.se/Sighting/136771250</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136065761</v>
+        <v>136771253</v>
       </c>
       <c r="B28" t="n">
-        <v>99152</v>
+        <v>99329</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,34 +3695,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223049</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721144</v>
+        <v>721181</v>
       </c>
       <c r="R28" t="n">
-        <v>6379285</v>
+        <v>6379245</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3610,12 +3758,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3629,7 +3782,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3646,7 +3799,6688 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136771253</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136771259</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>721191</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6379260</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771259</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136771261</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>721202</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6379264</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771261</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136771265</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>721221</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6379266</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771265</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136771271</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>721235</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6379245</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771271</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136771272</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>721242</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6379232</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771272</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136771281</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>721243</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6379246</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771281</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136771284</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>721233</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6379247</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771284</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136771286</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>721237</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6379248</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771286</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136771292</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>721235</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6379263</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771292</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136771293</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>721244</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6379282</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771293</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136771296</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>721250</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6379289</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771296</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136771297</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>721258</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6379292</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Dike 5 m S.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771297</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136771302</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>721257</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6379277</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771302</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136065751</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99331</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>721106</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6379184</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065751</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136065748</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99348</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>721106</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6379184</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065748</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136771234</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99374</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>721167</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6379301</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771234</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136065767</v>
+      </c>
+      <c r="B45" t="n">
+        <v>108363</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>721104</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6379290</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tätare skog med gran.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065767</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136065770</v>
+      </c>
+      <c r="B46" t="n">
+        <v>108363</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>721107</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6379284</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065770</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136065781</v>
+      </c>
+      <c r="B47" t="n">
+        <v>108363</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>721066</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6379261</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065781</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136065802</v>
+      </c>
+      <c r="B48" t="n">
+        <v>108363</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>721038</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6379233</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065802</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136771319</v>
+      </c>
+      <c r="B49" t="n">
+        <v>108368</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>721319</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6379237</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Tallskog på äldre strandvall med silikatsten.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771319</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136771320</v>
+      </c>
+      <c r="B50" t="n">
+        <v>108368</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>721330</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6379262</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Tallskog, grov.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771320</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136771321</v>
+      </c>
+      <c r="B51" t="n">
+        <v>108368</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>721337</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6379262</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Tallskog, grov.</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771321</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136771340</v>
+      </c>
+      <c r="B52" t="n">
+        <v>108368</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>721358</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6379295</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Lämplig miljö för alpnycklar.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Tallskog, grov.</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771340</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136065786</v>
+      </c>
+      <c r="B53" t="n">
+        <v>104881</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>721065</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6379250</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065786</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136065791</v>
+      </c>
+      <c r="B54" t="n">
+        <v>104881</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>721062</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6379242</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065791</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136065796</v>
+      </c>
+      <c r="B55" t="n">
+        <v>104881</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>721053</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6379240</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065796</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136771276</v>
+      </c>
+      <c r="B56" t="n">
+        <v>104886</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3);., Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>721257</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6379214</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771276</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136771336</v>
+      </c>
+      <c r="B57" t="n">
+        <v>104886</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>721383</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6379285</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Kalkglänta 25 x 25 m.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771336</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136065763</v>
+      </c>
+      <c r="B58" t="n">
+        <v>110326</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>721133</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6379293</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065763</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136771225</v>
+      </c>
+      <c r="B59" t="n">
+        <v>110331</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>721201</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6379288</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771225</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136771312</v>
+      </c>
+      <c r="B60" t="n">
+        <v>110331</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>721264</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6379267</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771312</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136065769</v>
+      </c>
+      <c r="B61" t="n">
+        <v>107057</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>721107</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6379284</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065769</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136771252</v>
+      </c>
+      <c r="B62" t="n">
+        <v>107062</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>721181</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6379245</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Högre träd.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771252</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136771267</v>
+      </c>
+      <c r="B63" t="n">
+        <v>107062</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>721235</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6379245</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771267</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136771291</v>
+      </c>
+      <c r="B64" t="n">
+        <v>107062</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>721235</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6379263</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Litet träd.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771291</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136771295</v>
+      </c>
+      <c r="B65" t="n">
+        <v>107062</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>721250</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6379289</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Småplantor.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved. Träden delvis på socklar.</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771295</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136065753</v>
+      </c>
+      <c r="B66" t="n">
+        <v>106383</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>721106</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6379184</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065753</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136065785</v>
+      </c>
+      <c r="B67" t="n">
+        <v>107764</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>721065</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6379250</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065785</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>136065790</v>
+      </c>
+      <c r="B68" t="n">
+        <v>107764</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>721062</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6379242</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065790</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>136771275</v>
+      </c>
+      <c r="B69" t="n">
+        <v>107769</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3);., Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>721257</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6379214</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771275</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136771335</v>
+      </c>
+      <c r="B70" t="n">
+        <v>107769</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>721383</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6379285</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Kalkglänta 25 x 25 m.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771335</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136065783</v>
+      </c>
+      <c r="B71" t="n">
+        <v>107305</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>721065</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6379250</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065783</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136065789</v>
+      </c>
+      <c r="B72" t="n">
+        <v>107305</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>721062</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6379242</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065789</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136771207</v>
+      </c>
+      <c r="B73" t="n">
+        <v>107310</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>721228</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6379313</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771207</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>136771333</v>
+      </c>
+      <c r="B74" t="n">
+        <v>107310</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>721383</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6379285</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Kalkglänta 25 x 25 m.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771333</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136065754</v>
+      </c>
+      <c r="B75" t="n">
+        <v>100400</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222662</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Axag</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Schoenus ferrugineus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>721106</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6379184</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136065754</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136065761</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99152</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>721144</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6379285</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136065761</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136771308</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99157</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>721264</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6379267</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771308</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136771210</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>721219</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6379304</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771210</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>136771216</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>721218</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6379288</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771216</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>136771228</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>721192</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6379281</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771228</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>136771245</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>721173</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6379274</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771245</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>136771249</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>721177</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6379254</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771249</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>136771257</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>721191</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6379260</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771257</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>136771270</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>721235</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6379245</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771270</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>136771280</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>721243</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6379246</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771280</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>136771353</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>721295</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6379310</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Blandskog frisk nära dike.</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771353</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>136771227</v>
+      </c>
+      <c r="B87" t="n">
+        <v>106479</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>721197</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6379286</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771227</t>
         </is>
       </c>
     </row>
@@ -3679,6 +10513,65 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100581</v>
+        <v>100583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100581</v>
+        <v>100583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100581</v>
+        <v>100583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100581</v>
+        <v>100583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>136771236</v>
       </c>
       <c r="B21" t="n">
-        <v>111649</v>
+        <v>111651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>136771218</v>
       </c>
       <c r="B25" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>136771219</v>
       </c>
       <c r="B26" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>136771250</v>
       </c>
       <c r="B27" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>136771253</v>
       </c>
       <c r="B28" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>136771259</v>
       </c>
       <c r="B29" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>136771261</v>
       </c>
       <c r="B30" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>136771265</v>
       </c>
       <c r="B31" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136771271</v>
       </c>
       <c r="B32" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>136771272</v>
       </c>
       <c r="B33" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>136771281</v>
       </c>
       <c r="B34" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>136771284</v>
       </c>
       <c r="B35" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136771286</v>
       </c>
       <c r="B36" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>136771292</v>
       </c>
       <c r="B37" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136771293</v>
       </c>
       <c r="B38" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>136771296</v>
       </c>
       <c r="B39" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>136771297</v>
       </c>
       <c r="B40" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>136771302</v>
       </c>
       <c r="B41" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>136771234</v>
       </c>
       <c r="B44" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>136771319</v>
       </c>
       <c r="B49" t="n">
-        <v>108368</v>
+        <v>108370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>136771320</v>
       </c>
       <c r="B50" t="n">
-        <v>108368</v>
+        <v>108370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>136771321</v>
       </c>
       <c r="B51" t="n">
-        <v>108368</v>
+        <v>108370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>136771340</v>
       </c>
       <c r="B52" t="n">
-        <v>108368</v>
+        <v>108370</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>136771276</v>
       </c>
       <c r="B56" t="n">
-        <v>104886</v>
+        <v>104888</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>136771336</v>
       </c>
       <c r="B57" t="n">
-        <v>104886</v>
+        <v>104888</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136771225</v>
       </c>
       <c r="B59" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>136771312</v>
       </c>
       <c r="B60" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>136771252</v>
       </c>
       <c r="B62" t="n">
-        <v>107062</v>
+        <v>107064</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>136771267</v>
       </c>
       <c r="B63" t="n">
-        <v>107062</v>
+        <v>107064</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>136771291</v>
       </c>
       <c r="B64" t="n">
-        <v>107062</v>
+        <v>107064</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136771295</v>
       </c>
       <c r="B65" t="n">
-        <v>107062</v>
+        <v>107064</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136771275</v>
       </c>
       <c r="B69" t="n">
-        <v>107769</v>
+        <v>107771</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>136771335</v>
       </c>
       <c r="B70" t="n">
-        <v>107769</v>
+        <v>107771</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136771207</v>
       </c>
       <c r="B73" t="n">
-        <v>107310</v>
+        <v>107312</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>136771333</v>
       </c>
       <c r="B74" t="n">
-        <v>107310</v>
+        <v>107312</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136771308</v>
       </c>
       <c r="B77" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>136771210</v>
       </c>
       <c r="B78" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>136771216</v>
       </c>
       <c r="B79" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>136771228</v>
       </c>
       <c r="B80" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>136771245</v>
       </c>
       <c r="B81" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>136771249</v>
       </c>
       <c r="B82" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>136771257</v>
       </c>
       <c r="B83" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136771270</v>
       </c>
       <c r="B84" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>136771280</v>
       </c>
       <c r="B85" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>136771353</v>
       </c>
       <c r="B86" t="n">
-        <v>99269</v>
+        <v>99271</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>136771227</v>
       </c>
       <c r="B87" t="n">
-        <v>106479</v>
+        <v>106481</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100583</v>
+        <v>100589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100583</v>
+        <v>100589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100583</v>
+        <v>100589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100583</v>
+        <v>100589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>136771236</v>
       </c>
       <c r="B21" t="n">
-        <v>111651</v>
+        <v>111657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>136771218</v>
       </c>
       <c r="B25" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>136771219</v>
       </c>
       <c r="B26" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>136771250</v>
       </c>
       <c r="B27" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>136771253</v>
       </c>
       <c r="B28" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>136771259</v>
       </c>
       <c r="B29" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>136771261</v>
       </c>
       <c r="B30" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>136771265</v>
       </c>
       <c r="B31" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136771271</v>
       </c>
       <c r="B32" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>136771272</v>
       </c>
       <c r="B33" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>136771281</v>
       </c>
       <c r="B34" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>136771284</v>
       </c>
       <c r="B35" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136771286</v>
       </c>
       <c r="B36" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>136771292</v>
       </c>
       <c r="B37" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136771293</v>
       </c>
       <c r="B38" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>136771296</v>
       </c>
       <c r="B39" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>136771297</v>
       </c>
       <c r="B40" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>136771302</v>
       </c>
       <c r="B41" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>136771234</v>
       </c>
       <c r="B44" t="n">
-        <v>99376</v>
+        <v>99382</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>136771319</v>
       </c>
       <c r="B49" t="n">
-        <v>108370</v>
+        <v>108376</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>136771320</v>
       </c>
       <c r="B50" t="n">
-        <v>108370</v>
+        <v>108376</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>136771321</v>
       </c>
       <c r="B51" t="n">
-        <v>108370</v>
+        <v>108376</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>136771340</v>
       </c>
       <c r="B52" t="n">
-        <v>108370</v>
+        <v>108376</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>136771276</v>
       </c>
       <c r="B56" t="n">
-        <v>104888</v>
+        <v>104894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>136771336</v>
       </c>
       <c r="B57" t="n">
-        <v>104888</v>
+        <v>104894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136771225</v>
       </c>
       <c r="B59" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>136771312</v>
       </c>
       <c r="B60" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>136771252</v>
       </c>
       <c r="B62" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>136771267</v>
       </c>
       <c r="B63" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>136771291</v>
       </c>
       <c r="B64" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136771295</v>
       </c>
       <c r="B65" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136771275</v>
       </c>
       <c r="B69" t="n">
-        <v>107771</v>
+        <v>107777</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>136771335</v>
       </c>
       <c r="B70" t="n">
-        <v>107771</v>
+        <v>107777</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136771207</v>
       </c>
       <c r="B73" t="n">
-        <v>107312</v>
+        <v>107318</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>136771333</v>
       </c>
       <c r="B74" t="n">
-        <v>107312</v>
+        <v>107318</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136771308</v>
       </c>
       <c r="B77" t="n">
-        <v>99159</v>
+        <v>99165</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>136771210</v>
       </c>
       <c r="B78" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>136771216</v>
       </c>
       <c r="B79" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>136771228</v>
       </c>
       <c r="B80" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>136771245</v>
       </c>
       <c r="B81" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>136771249</v>
       </c>
       <c r="B82" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>136771257</v>
       </c>
       <c r="B83" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136771270</v>
       </c>
       <c r="B84" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>136771280</v>
       </c>
       <c r="B85" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>136771353</v>
       </c>
       <c r="B86" t="n">
-        <v>99271</v>
+        <v>99277</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>136771227</v>
       </c>
       <c r="B87" t="n">
-        <v>106481</v>
+        <v>106487</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100589</v>
+        <v>100591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100589</v>
+        <v>100591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100589</v>
+        <v>100591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100589</v>
+        <v>100591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>136771236</v>
       </c>
       <c r="B21" t="n">
-        <v>111657</v>
+        <v>111659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>136771218</v>
       </c>
       <c r="B25" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>136771219</v>
       </c>
       <c r="B26" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>136771250</v>
       </c>
       <c r="B27" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>136771253</v>
       </c>
       <c r="B28" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>136771259</v>
       </c>
       <c r="B29" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>136771261</v>
       </c>
       <c r="B30" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>136771265</v>
       </c>
       <c r="B31" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>136771271</v>
       </c>
       <c r="B32" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>136771272</v>
       </c>
       <c r="B33" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>136771281</v>
       </c>
       <c r="B34" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>136771284</v>
       </c>
       <c r="B35" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136771286</v>
       </c>
       <c r="B36" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>136771292</v>
       </c>
       <c r="B37" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>136771293</v>
       </c>
       <c r="B38" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>136771296</v>
       </c>
       <c r="B39" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>136771297</v>
       </c>
       <c r="B40" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>136771302</v>
       </c>
       <c r="B41" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>136771234</v>
       </c>
       <c r="B44" t="n">
-        <v>99382</v>
+        <v>99384</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>136771319</v>
       </c>
       <c r="B49" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>136771320</v>
       </c>
       <c r="B50" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>136771321</v>
       </c>
       <c r="B51" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>136771340</v>
       </c>
       <c r="B52" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>136771276</v>
       </c>
       <c r="B56" t="n">
-        <v>104894</v>
+        <v>104896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>136771336</v>
       </c>
       <c r="B57" t="n">
-        <v>104894</v>
+        <v>104896</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>136771225</v>
       </c>
       <c r="B59" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>136771312</v>
       </c>
       <c r="B60" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>136771252</v>
       </c>
       <c r="B62" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>136771267</v>
       </c>
       <c r="B63" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>136771291</v>
       </c>
       <c r="B64" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>136771295</v>
       </c>
       <c r="B65" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>136771275</v>
       </c>
       <c r="B69" t="n">
-        <v>107777</v>
+        <v>107779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>136771335</v>
       </c>
       <c r="B70" t="n">
-        <v>107777</v>
+        <v>107779</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>136771207</v>
       </c>
       <c r="B73" t="n">
-        <v>107318</v>
+        <v>107320</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>136771333</v>
       </c>
       <c r="B74" t="n">
-        <v>107318</v>
+        <v>107320</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>136771308</v>
       </c>
       <c r="B77" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>136771210</v>
       </c>
       <c r="B78" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>136771216</v>
       </c>
       <c r="B79" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>136771228</v>
       </c>
       <c r="B80" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>136771245</v>
       </c>
       <c r="B81" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>136771249</v>
       </c>
       <c r="B82" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>136771257</v>
       </c>
       <c r="B83" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136771270</v>
       </c>
       <c r="B84" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>136771280</v>
       </c>
       <c r="B85" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>136771353</v>
       </c>
       <c r="B86" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>136771227</v>
       </c>
       <c r="B87" t="n">
-        <v>106487</v>
+        <v>106489</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,53 +1144,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136065647</v>
+        <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>58003</v>
+        <v>87415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721143</v>
+        <v>721259</v>
       </c>
       <c r="R6" t="n">
-        <v>6379301</v>
+        <v>6379282</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,17 +1209,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Granlågor med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,79 +1235,69 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065647</t>
+          <t>https://artportalen.se/Sighting/137090260</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136065648</v>
+        <v>137090253</v>
       </c>
       <c r="B7" t="n">
-        <v>58003</v>
+        <v>91550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>3286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>721106</v>
+        <v>721141</v>
       </c>
       <c r="R7" t="n">
-        <v>6379267</v>
+        <v>6379284</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,17 +1321,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,36 +1347,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065648</t>
+          <t>https://artportalen.se/Sighting/137090253</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136065649</v>
+        <v>137090256</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>87594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,42 +1379,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>3624</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721105</v>
+        <v>721216</v>
       </c>
       <c r="R8" t="n">
-        <v>6379264</v>
+        <v>6379267</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,17 +1429,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,36 +1455,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065649</t>
+          <t>https://artportalen.se/Sighting/137090256</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136065650</v>
+        <v>137090255</v>
       </c>
       <c r="B9" t="n">
-        <v>58003</v>
+        <v>87491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,42 +1487,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721083</v>
+        <v>721193</v>
       </c>
       <c r="R9" t="n">
-        <v>6379258</v>
+        <v>6379266</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,17 +1541,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,36 +1567,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065650</t>
+          <t>https://artportalen.se/Sighting/137090255</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136065651</v>
+        <v>137090258</v>
       </c>
       <c r="B10" t="n">
-        <v>58003</v>
+        <v>87491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,42 +1599,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>721066</v>
+        <v>721214</v>
       </c>
       <c r="R10" t="n">
-        <v>6379261</v>
+        <v>6379294</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,17 +1653,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,36 +1679,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065651</t>
+          <t>https://artportalen.se/Sighting/137090258</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136065652</v>
+        <v>137090259</v>
       </c>
       <c r="B11" t="n">
-        <v>58003</v>
+        <v>87491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,42 +1711,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721058</v>
+        <v>721257</v>
       </c>
       <c r="R11" t="n">
-        <v>6379242</v>
+        <v>6379298</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,17 +1765,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,36 +1791,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065652</t>
+          <t>https://artportalen.se/Sighting/137090259</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136774891</v>
+        <v>137090261</v>
       </c>
       <c r="B12" t="n">
-        <v>58005</v>
+        <v>87491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,42 +1823,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721203</v>
+        <v>721155</v>
       </c>
       <c r="R12" t="n">
-        <v>6379231</v>
+        <v>6379241</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1916,17 +1877,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Död gran något S koordinat med insektshål och med äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,36 +1903,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774891</t>
+          <t>https://artportalen.se/Sighting/137090261</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136774892</v>
+        <v>137090263</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>87491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,39 +1935,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721257</v>
+        <v>721085</v>
       </c>
       <c r="R13" t="n">
-        <v>6379277</v>
+        <v>6379250</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2033,17 +1989,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Grov, död stånde tall, insektsangripen, med äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,36 +2015,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774892</t>
+          <t>https://artportalen.se/Sighting/137090263</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136774893</v>
+        <v>137090314</v>
       </c>
       <c r="B14" t="n">
-        <v>58005</v>
+        <v>87491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,42 +2047,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>A 33289-2026 Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>721264</v>
+        <v>721215</v>
       </c>
       <c r="R14" t="n">
-        <v>6379267</v>
+        <v>6379262</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2150,17 +2104,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gran, död,  låga med gott om insektshål med äldre födosök av spillkråka. Grov, död stånde tall, insektsangripen, med äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,81 +2128,75 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774893</t>
+          <t>https://artportalen.se/Sighting/137090314</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136774894</v>
+        <v>137090316</v>
       </c>
       <c r="B15" t="n">
-        <v>58005</v>
+        <v>87352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>A 33289-2026 Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>721290</v>
+        <v>721258</v>
       </c>
       <c r="R15" t="n">
-        <v>6379243</v>
+        <v>6379310</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,17 +2220,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Granar, 4 st. döda,  med gott om insektshål med äldre födosök av spillkråka.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,38 +2244,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774894</t>
+          <t>https://artportalen.se/Sighting/137090316</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136774895</v>
+        <v>136065647</v>
       </c>
       <c r="B16" t="n">
-        <v>58005</v>
+        <v>58003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,14 +2304,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>721296</v>
+        <v>721143</v>
       </c>
       <c r="R16" t="n">
-        <v>6379235</v>
+        <v>6379301</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2384,17 +2338,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Granlåga med gott om insektshål med äldre födosök av spillkråka. Dessutom en död stående.</t>
+          <t>Granlågor med gott om insektshål; äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,16 +2379,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774895</t>
+          <t>https://artportalen.se/Sighting/136065647</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136774896</v>
+        <v>136065648</v>
       </c>
       <c r="B17" t="n">
-        <v>58005</v>
+        <v>58003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,19 +2416,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>721314</v>
+        <v>721106</v>
       </c>
       <c r="R17" t="n">
-        <v>6379233</v>
+        <v>6379267</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2501,17 +2455,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Granlågor 2 med insektshål, varav båda har födosökts av spillkråka.</t>
+          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,7 +2479,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallskog på äldre strandvall med silikatsten.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2542,16 +2496,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774896</t>
+          <t>https://artportalen.se/Sighting/136065648</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136774897</v>
+        <v>136065649</v>
       </c>
       <c r="B18" t="n">
-        <v>58005</v>
+        <v>58003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2584,14 +2538,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>721357</v>
+        <v>721105</v>
       </c>
       <c r="R18" t="n">
-        <v>6379269</v>
+        <v>6379264</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2618,17 +2572,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Grov, död tall, insektsangripen, liggande i luften med stödgrenar mot mark. Med äldre födosök av spillkråka.</t>
+          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,16 +2613,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774897</t>
+          <t>https://artportalen.se/Sighting/136065649</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136774898</v>
+        <v>136065650</v>
       </c>
       <c r="B19" t="n">
-        <v>58005</v>
+        <v>58003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,14 +2655,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>721305</v>
+        <v>721083</v>
       </c>
       <c r="R19" t="n">
-        <v>6379306</v>
+        <v>6379258</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2735,17 +2689,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Födosök i 2 döda granar med insektsangrepp.</t>
+          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,16 +2730,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774898</t>
+          <t>https://artportalen.se/Sighting/136065650</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136774899</v>
+        <v>136065651</v>
       </c>
       <c r="B20" t="n">
-        <v>58005</v>
+        <v>58003</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,14 +2772,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721315</v>
+        <v>721066</v>
       </c>
       <c r="R20" t="n">
-        <v>6379289</v>
+        <v>6379261</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2852,17 +2806,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Födosök (äldre) i grov, död tall med insektsangrepp.</t>
+          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2893,60 +2847,56 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774899</t>
+          <t>https://artportalen.se/Sighting/136065651</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136771236</v>
+        <v>136065652</v>
       </c>
       <c r="B21" t="n">
-        <v>111659</v>
+        <v>58003</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>721167</v>
+        <v>721058</v>
       </c>
       <c r="R21" t="n">
-        <v>6379301</v>
+        <v>6379242</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2973,12 +2923,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Död, stående tall med gott om insektshål; äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2992,7 +2947,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3009,54 +2964,59 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771236</t>
+          <t>https://artportalen.se/Sighting/136065652</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136065801</v>
+        <v>136774891</v>
       </c>
       <c r="B22" t="n">
-        <v>111659</v>
+        <v>58005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219719</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Säfferot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Seseli libanotis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) W. D. J. Koch</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>721038</v>
+        <v>721203</v>
       </c>
       <c r="R22" t="n">
-        <v>6379233</v>
+        <v>6379231</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3080,12 +3040,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Död gran något S koordinat med insektshål och med äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,7 +3064,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3116,16 +3081,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065801</t>
+          <t>https://artportalen.se/Sighting/136774891</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136065749</v>
+        <v>136774892</v>
       </c>
       <c r="B23" t="n">
-        <v>99321</v>
+        <v>58005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3133,37 +3098,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219797</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>721106</v>
+        <v>721257</v>
       </c>
       <c r="R23" t="n">
-        <v>6379184</v>
+        <v>6379277</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3187,12 +3157,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Grov, död stånde tall, insektsangripen, med äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3206,7 +3181,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3223,16 +3198,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065749</t>
+          <t>https://artportalen.se/Sighting/136774892</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136065750</v>
+        <v>136774893</v>
       </c>
       <c r="B24" t="n">
-        <v>99324</v>
+        <v>58005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,37 +3215,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721106</v>
+        <v>721264</v>
       </c>
       <c r="R24" t="n">
-        <v>6379184</v>
+        <v>6379267</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3294,12 +3274,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gran, död,  låga med gott om insektshål med äldre födosök av spillkråka. Grov, död stånde tall, insektsangripen, med äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3313,7 +3298,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3330,16 +3315,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065750</t>
+          <t>https://artportalen.se/Sighting/136774893</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136771218</v>
+        <v>136774894</v>
       </c>
       <c r="B25" t="n">
-        <v>99339</v>
+        <v>58005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,31 +3332,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3380,13 +3361,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721212</v>
+        <v>721290</v>
       </c>
       <c r="R25" t="n">
-        <v>6379283</v>
+        <v>6379243</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3418,6 +3399,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Granar, 4 st. döda,  med gott om insektshål med äldre födosök av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3429,7 +3415,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3446,16 +3432,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771218</t>
+          <t>https://artportalen.se/Sighting/136774894</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136771219</v>
+        <v>136774895</v>
       </c>
       <c r="B26" t="n">
-        <v>99339</v>
+        <v>58005</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,31 +3449,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3496,10 +3478,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721206</v>
+        <v>721296</v>
       </c>
       <c r="R26" t="n">
-        <v>6379274</v>
+        <v>6379235</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3534,6 +3516,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Granlåga med gott om insektshål med äldre födosök av spillkråka. Dessutom en död stående.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3545,7 +3532,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3562,16 +3549,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771219</t>
+          <t>https://artportalen.se/Sighting/136774895</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136771250</v>
+        <v>136774896</v>
       </c>
       <c r="B27" t="n">
-        <v>99339</v>
+        <v>58005</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3579,31 +3566,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3612,10 +3595,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721177</v>
+        <v>721314</v>
       </c>
       <c r="R27" t="n">
-        <v>6379254</v>
+        <v>6379233</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3650,6 +3633,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Granlågor 2 med insektshål, varav båda har födosökts av spillkråka.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3661,7 +3649,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+          <t>Tallskog på äldre strandvall med silikatsten.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3678,16 +3666,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771250</t>
+          <t>https://artportalen.se/Sighting/136774896</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136771253</v>
+        <v>136774897</v>
       </c>
       <c r="B28" t="n">
-        <v>99339</v>
+        <v>58005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3695,31 +3683,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3728,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>721181</v>
+        <v>721357</v>
       </c>
       <c r="R28" t="n">
-        <v>6379245</v>
+        <v>6379269</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3768,7 +3752,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Dike NV.</t>
+          <t>Grov, död tall, insektsangripen, liggande i luften med stödgrenar mot mark. Med äldre födosök av spillkråka.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,7 +3766,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3799,16 +3783,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771253</t>
+          <t>https://artportalen.se/Sighting/136774897</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136771259</v>
+        <v>136774898</v>
       </c>
       <c r="B29" t="n">
-        <v>99339</v>
+        <v>58005</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3816,31 +3800,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3849,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>721191</v>
+        <v>721305</v>
       </c>
       <c r="R29" t="n">
-        <v>6379260</v>
+        <v>6379306</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3889,7 +3869,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Dike NV.</t>
+          <t>Födosök i 2 döda granar med insektsangrepp.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,7 +3883,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3920,16 +3900,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771259</t>
+          <t>https://artportalen.se/Sighting/136774898</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136771261</v>
+        <v>136774899</v>
       </c>
       <c r="B30" t="n">
-        <v>99339</v>
+        <v>58005</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3937,31 +3917,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3970,10 +3946,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>721202</v>
+        <v>721315</v>
       </c>
       <c r="R30" t="n">
-        <v>6379264</v>
+        <v>6379289</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4010,7 +3986,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Dike NV.</t>
+          <t>Födosök (äldre) i grov, död tall med insektsangrepp.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4024,7 +4000,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4041,43 +4017,43 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771261</t>
+          <t>https://artportalen.se/Sighting/136774899</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136771265</v>
+        <v>136771236</v>
       </c>
       <c r="B31" t="n">
-        <v>99339</v>
+        <v>111659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4091,10 +4067,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>721221</v>
+        <v>721167</v>
       </c>
       <c r="R31" t="n">
-        <v>6379266</v>
+        <v>6379301</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4129,11 +4105,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Dike NV.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4162,60 +4133,51 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771265</t>
+          <t>https://artportalen.se/Sighting/136771236</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136771271</v>
+        <v>136065801</v>
       </c>
       <c r="B32" t="n">
-        <v>99339</v>
+        <v>111659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>219719</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Säfferot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Seseli libanotis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>721235</v>
+        <v>721038</v>
       </c>
       <c r="R32" t="n">
-        <v>6379245</v>
+        <v>6379233</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4242,12 +4204,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4261,7 +4223,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4278,16 +4240,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771271</t>
+          <t>https://artportalen.se/Sighting/136065801</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136771272</v>
+        <v>136065749</v>
       </c>
       <c r="B33" t="n">
-        <v>99339</v>
+        <v>99321</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4295,46 +4257,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721242</v>
+        <v>721106</v>
       </c>
       <c r="R33" t="n">
-        <v>6379232</v>
+        <v>6379184</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4358,12 +4311,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4377,7 +4330,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4394,16 +4347,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771272</t>
+          <t>https://artportalen.se/Sighting/136065749</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136771281</v>
+        <v>136065750</v>
       </c>
       <c r="B34" t="n">
-        <v>99339</v>
+        <v>99324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4428,29 +4381,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>721243</v>
+        <v>721106</v>
       </c>
       <c r="R34" t="n">
-        <v>6379246</v>
+        <v>6379184</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4474,12 +4418,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4493,7 +4437,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4510,13 +4454,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771281</t>
+          <t>https://artportalen.se/Sighting/136065750</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136771284</v>
+        <v>136771218</v>
       </c>
       <c r="B35" t="n">
         <v>99339</v>
@@ -4546,7 +4490,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4560,10 +4504,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>721233</v>
+        <v>721212</v>
       </c>
       <c r="R35" t="n">
-        <v>6379247</v>
+        <v>6379283</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4609,7 +4553,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4626,13 +4570,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771284</t>
+          <t>https://artportalen.se/Sighting/136771218</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136771286</v>
+        <v>136771219</v>
       </c>
       <c r="B36" t="n">
         <v>99339</v>
@@ -4662,7 +4606,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4676,10 +4620,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>721237</v>
+        <v>721206</v>
       </c>
       <c r="R36" t="n">
-        <v>6379248</v>
+        <v>6379274</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4725,7 +4669,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4742,13 +4686,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771286</t>
+          <t>https://artportalen.se/Sighting/136771219</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136771292</v>
+        <v>136771250</v>
       </c>
       <c r="B37" t="n">
         <v>99339</v>
@@ -4792,10 +4736,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>721235</v>
+        <v>721177</v>
       </c>
       <c r="R37" t="n">
-        <v>6379263</v>
+        <v>6379254</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4841,7 +4785,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4858,13 +4802,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771292</t>
+          <t>https://artportalen.se/Sighting/136771250</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136771293</v>
+        <v>136771253</v>
       </c>
       <c r="B38" t="n">
         <v>99339</v>
@@ -4894,7 +4838,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4908,10 +4852,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>721244</v>
+        <v>721181</v>
       </c>
       <c r="R38" t="n">
-        <v>6379282</v>
+        <v>6379245</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4946,6 +4890,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4974,13 +4923,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771293</t>
+          <t>https://artportalen.se/Sighting/136771253</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136771296</v>
+        <v>136771259</v>
       </c>
       <c r="B39" t="n">
         <v>99339</v>
@@ -5010,7 +4959,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5018,21 +4967,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>721250</v>
+        <v>721191</v>
       </c>
       <c r="R39" t="n">
-        <v>6379289</v>
+        <v>6379260</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5067,6 +5011,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5095,13 +5044,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771296</t>
+          <t>https://artportalen.se/Sighting/136771259</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136771297</v>
+        <v>136771261</v>
       </c>
       <c r="B40" t="n">
         <v>99339</v>
@@ -5131,7 +5080,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5145,10 +5094,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>721258</v>
+        <v>721202</v>
       </c>
       <c r="R40" t="n">
-        <v>6379292</v>
+        <v>6379264</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5185,7 +5134,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Dike 5 m S.</t>
+          <t>Dike NV.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5216,13 +5165,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771297</t>
+          <t>https://artportalen.se/Sighting/136771261</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136771302</v>
+        <v>136771265</v>
       </c>
       <c r="B41" t="n">
         <v>99339</v>
@@ -5252,7 +5201,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5266,10 +5215,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>721257</v>
+        <v>721221</v>
       </c>
       <c r="R41" t="n">
-        <v>6379277</v>
+        <v>6379266</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5304,6 +5253,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5315,7 +5269,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5332,16 +5286,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771302</t>
+          <t>https://artportalen.se/Sighting/136771265</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136065751</v>
+        <v>136771271</v>
       </c>
       <c r="B42" t="n">
-        <v>99331</v>
+        <v>99339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5349,16 +5303,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5366,20 +5320,29 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>721106</v>
+        <v>721235</v>
       </c>
       <c r="R42" t="n">
-        <v>6379184</v>
+        <v>6379245</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5403,12 +5366,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5422,7 +5385,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5439,16 +5402,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065751</t>
+          <t>https://artportalen.se/Sighting/136771271</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136065748</v>
+        <v>136771272</v>
       </c>
       <c r="B43" t="n">
-        <v>99348</v>
+        <v>99339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5456,37 +5419,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>721106</v>
+        <v>721242</v>
       </c>
       <c r="R43" t="n">
-        <v>6379184</v>
+        <v>6379232</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5510,12 +5482,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5529,7 +5501,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5546,16 +5518,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065748</t>
+          <t>https://artportalen.se/Sighting/136771272</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136771234</v>
+        <v>136771281</v>
       </c>
       <c r="B44" t="n">
-        <v>99384</v>
+        <v>99339</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5563,26 +5535,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5590,21 +5562,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721167</v>
+        <v>721243</v>
       </c>
       <c r="R44" t="n">
-        <v>6379301</v>
+        <v>6379246</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5667,43 +5634,43 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771234</t>
+          <t>https://artportalen.se/Sighting/136771281</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136065767</v>
+        <v>136771284</v>
       </c>
       <c r="B45" t="n">
-        <v>108363</v>
+        <v>99339</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5713,14 +5680,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>721104</v>
+        <v>721233</v>
       </c>
       <c r="R45" t="n">
-        <v>6379290</v>
+        <v>6379247</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5747,17 +5714,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tätare skog med gran.</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5771,7 +5733,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5788,43 +5750,43 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065767</t>
+          <t>https://artportalen.se/Sighting/136771284</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136065770</v>
+        <v>136771286</v>
       </c>
       <c r="B46" t="n">
-        <v>108363</v>
+        <v>99339</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5834,14 +5796,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>721107</v>
+        <v>721237</v>
       </c>
       <c r="R46" t="n">
-        <v>6379284</v>
+        <v>6379248</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5868,12 +5830,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5887,7 +5849,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5904,51 +5866,60 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065770</t>
+          <t>https://artportalen.se/Sighting/136771286</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136065781</v>
+        <v>136771292</v>
       </c>
       <c r="B47" t="n">
-        <v>108363</v>
+        <v>99339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>721066</v>
+        <v>721235</v>
       </c>
       <c r="R47" t="n">
-        <v>6379261</v>
+        <v>6379263</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5975,12 +5946,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5994,7 +5965,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6011,51 +5982,60 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065781</t>
+          <t>https://artportalen.se/Sighting/136771292</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136065802</v>
+        <v>136771293</v>
       </c>
       <c r="B48" t="n">
-        <v>108363</v>
+        <v>99339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>721038</v>
+        <v>721244</v>
       </c>
       <c r="R48" t="n">
-        <v>6379233</v>
+        <v>6379282</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6082,12 +6062,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6101,7 +6081,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6118,43 +6098,43 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065802</t>
+          <t>https://artportalen.se/Sighting/136771293</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136771319</v>
+        <v>136771296</v>
       </c>
       <c r="B49" t="n">
-        <v>108378</v>
+        <v>99339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6162,16 +6142,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>721319</v>
+        <v>721250</v>
       </c>
       <c r="R49" t="n">
-        <v>6379237</v>
+        <v>6379289</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6217,7 +6202,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Tallskog på äldre strandvall med silikatsten.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6234,38 +6219,38 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771319</t>
+          <t>https://artportalen.se/Sighting/136771296</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136771320</v>
+        <v>136771297</v>
       </c>
       <c r="B50" t="n">
-        <v>108378</v>
+        <v>99339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6284,10 +6269,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>721330</v>
+        <v>721258</v>
       </c>
       <c r="R50" t="n">
-        <v>6379262</v>
+        <v>6379292</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6322,6 +6307,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Dike 5 m S.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6333,7 +6323,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Tallskog, grov.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6350,43 +6340,43 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771320</t>
+          <t>https://artportalen.se/Sighting/136771297</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136771321</v>
+        <v>136771302</v>
       </c>
       <c r="B51" t="n">
-        <v>108378</v>
+        <v>99339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6400,10 +6390,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>721337</v>
+        <v>721257</v>
       </c>
       <c r="R51" t="n">
-        <v>6379262</v>
+        <v>6379277</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6449,7 +6439,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Tallskog, grov.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6466,63 +6456,54 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771321</t>
+          <t>https://artportalen.se/Sighting/136771302</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136771340</v>
+        <v>136065751</v>
       </c>
       <c r="B52" t="n">
-        <v>108378</v>
+        <v>99331</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>219799</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>721358</v>
+        <v>721106</v>
       </c>
       <c r="R52" t="n">
-        <v>6379295</v>
+        <v>6379184</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6546,17 +6527,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Lämplig miljö för alpnycklar.</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6570,7 +6546,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Tallskog, grov.</t>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6587,38 +6563,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771340</t>
+          <t>https://artportalen.se/Sighting/136065751</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136065786</v>
+        <v>136065748</v>
       </c>
       <c r="B53" t="n">
-        <v>104881</v>
+        <v>99348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220164</v>
+        <v>219811</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6628,13 +6604,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721065</v>
+        <v>721106</v>
       </c>
       <c r="R53" t="n">
-        <v>6379250</v>
+        <v>6379184</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6677,7 +6653,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6694,51 +6670,65 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065786</t>
+          <t>https://artportalen.se/Sighting/136065748</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136065791</v>
+        <v>136771234</v>
       </c>
       <c r="B54" t="n">
-        <v>104881</v>
+        <v>99384</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220164</v>
+        <v>219862</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>721062</v>
+        <v>721167</v>
       </c>
       <c r="R54" t="n">
-        <v>6379242</v>
+        <v>6379301</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6765,12 +6755,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6784,7 +6774,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6801,54 +6791,54 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065791</t>
+          <t>https://artportalen.se/Sighting/136771234</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136065796</v>
+        <v>137090254</v>
       </c>
       <c r="B55" t="n">
-        <v>104881</v>
+        <v>99384</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220164</v>
+        <v>219862</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>721053</v>
+        <v>721141</v>
       </c>
       <c r="R55" t="n">
-        <v>6379240</v>
+        <v>6379284</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6872,12 +6862,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6888,36 +6888,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065796</t>
+          <t>https://artportalen.se/Sighting/137090254</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136771276</v>
+        <v>136065767</v>
       </c>
       <c r="B56" t="n">
-        <v>104896</v>
+        <v>108363</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6925,34 +6920,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3);., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>721257</v>
+        <v>721104</v>
       </c>
       <c r="R56" t="n">
-        <v>6379214</v>
+        <v>6379290</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6979,12 +6983,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Tätare skog med gran.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6998,7 +7007,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7015,16 +7024,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771276</t>
+          <t>https://artportalen.se/Sighting/136065767</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136771336</v>
+        <v>136065770</v>
       </c>
       <c r="B57" t="n">
-        <v>104896</v>
+        <v>108363</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7032,37 +7041,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721383</v>
+        <v>721107</v>
       </c>
       <c r="R57" t="n">
-        <v>6379285</v>
+        <v>6379284</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7086,17 +7104,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kalkglänta 25 x 25 m.</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7110,7 +7123,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7127,16 +7140,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771336</t>
+          <t>https://artportalen.se/Sighting/136065770</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136065763</v>
+        <v>136065781</v>
       </c>
       <c r="B58" t="n">
-        <v>110326</v>
+        <v>108363</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7144,21 +7157,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7168,10 +7181,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721133</v>
+        <v>721066</v>
       </c>
       <c r="R58" t="n">
-        <v>6379293</v>
+        <v>6379261</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7217,7 +7230,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7234,16 +7247,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065763</t>
+          <t>https://artportalen.se/Sighting/136065781</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136771225</v>
+        <v>136065802</v>
       </c>
       <c r="B59" t="n">
-        <v>110341</v>
+        <v>108363</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7251,34 +7264,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>721201</v>
+        <v>721038</v>
       </c>
       <c r="R59" t="n">
-        <v>6379288</v>
+        <v>6379233</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7305,12 +7318,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7324,7 +7337,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7341,16 +7354,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771225</t>
+          <t>https://artportalen.se/Sighting/136065802</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136771312</v>
+        <v>136771319</v>
       </c>
       <c r="B60" t="n">
-        <v>110341</v>
+        <v>108378</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7358,37 +7371,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>721264</v>
+        <v>721319</v>
       </c>
       <c r="R60" t="n">
-        <v>6379267</v>
+        <v>6379237</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7431,7 +7453,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Tallskog på äldre strandvall med silikatsten.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7448,51 +7470,60 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771312</t>
+          <t>https://artportalen.se/Sighting/136771319</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136065769</v>
+        <v>136771320</v>
       </c>
       <c r="B61" t="n">
-        <v>107057</v>
+        <v>108378</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>721107</v>
+        <v>721330</v>
       </c>
       <c r="R61" t="n">
-        <v>6379284</v>
+        <v>6379262</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7519,12 +7550,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7538,7 +7569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles.</t>
+          <t>Tallskog, grov.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7555,43 +7586,43 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065769</t>
+          <t>https://artportalen.se/Sighting/136771320</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136771252</v>
+        <v>136771321</v>
       </c>
       <c r="B62" t="n">
-        <v>107072</v>
+        <v>108378</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7605,10 +7636,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>721181</v>
+        <v>721337</v>
       </c>
       <c r="R62" t="n">
-        <v>6379245</v>
+        <v>6379262</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7643,11 +7674,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Högre träd.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7659,7 +7685,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Tallskog, grov.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7676,51 +7702,60 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771252</t>
+          <t>https://artportalen.se/Sighting/136771321</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136771267</v>
+        <v>136771340</v>
       </c>
       <c r="B63" t="n">
-        <v>107072</v>
+        <v>108378</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>721235</v>
+        <v>721358</v>
       </c>
       <c r="R63" t="n">
-        <v>6379245</v>
+        <v>6379295</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7755,6 +7790,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Lämplig miljö för alpnycklar.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7766,7 +7806,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Tallskog, grov.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7783,60 +7823,51 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771267</t>
+          <t>https://artportalen.se/Sighting/136771340</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136771291</v>
+        <v>136065786</v>
       </c>
       <c r="B64" t="n">
-        <v>107072</v>
+        <v>104881</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220785</v>
+        <v>220164</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>721235</v>
+        <v>721065</v>
       </c>
       <c r="R64" t="n">
-        <v>6379263</v>
+        <v>6379250</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7863,17 +7894,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Litet träd.</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7887,7 +7913,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7904,51 +7930,51 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771291</t>
+          <t>https://artportalen.se/Sighting/136065786</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136771295</v>
+        <v>136065791</v>
       </c>
       <c r="B65" t="n">
-        <v>107072</v>
+        <v>104881</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220785</v>
+        <v>220164</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>721250</v>
+        <v>721062</v>
       </c>
       <c r="R65" t="n">
-        <v>6379289</v>
+        <v>6379242</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7975,17 +8001,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Småplantor.</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7999,7 +8020,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved. Träden delvis på socklar.</t>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8016,16 +8037,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771295</t>
+          <t>https://artportalen.se/Sighting/136065791</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136065753</v>
+        <v>136065796</v>
       </c>
       <c r="B66" t="n">
-        <v>106383</v>
+        <v>104881</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8033,21 +8054,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221137</v>
+        <v>220164</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8057,13 +8078,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>721106</v>
+        <v>721053</v>
       </c>
       <c r="R66" t="n">
-        <v>6379184</v>
+        <v>6379240</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8106,7 +8127,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8123,16 +8144,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065753</t>
+          <t>https://artportalen.se/Sighting/136065796</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136065785</v>
+        <v>136771276</v>
       </c>
       <c r="B67" t="n">
-        <v>107764</v>
+        <v>104896</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8140,34 +8161,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3);., Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>721065</v>
+        <v>721257</v>
       </c>
       <c r="R67" t="n">
-        <v>6379250</v>
+        <v>6379214</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8194,12 +8215,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8213,7 +8234,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8230,16 +8251,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065785</t>
+          <t>https://artportalen.se/Sighting/136771276</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136065790</v>
+        <v>136771336</v>
       </c>
       <c r="B68" t="n">
-        <v>107764</v>
+        <v>104896</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8247,37 +8268,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>721062</v>
+        <v>721383</v>
       </c>
       <c r="R68" t="n">
-        <v>6379242</v>
+        <v>6379285</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8301,12 +8322,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Kalkglänta 25 x 25 m.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8320,7 +8346,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8337,16 +8363,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065790</t>
+          <t>https://artportalen.se/Sighting/136771336</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136771275</v>
+        <v>136065763</v>
       </c>
       <c r="B69" t="n">
-        <v>107779</v>
+        <v>110326</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8354,16 +8380,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8374,14 +8400,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3);., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>721257</v>
+        <v>721133</v>
       </c>
       <c r="R69" t="n">
-        <v>6379214</v>
+        <v>6379293</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8408,12 +8434,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8427,7 +8453,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8444,16 +8470,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771275</t>
+          <t>https://artportalen.se/Sighting/136065763</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136771335</v>
+        <v>136771225</v>
       </c>
       <c r="B70" t="n">
-        <v>107779</v>
+        <v>110341</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8461,16 +8487,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8485,13 +8511,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>721383</v>
+        <v>721201</v>
       </c>
       <c r="R70" t="n">
-        <v>6379285</v>
+        <v>6379288</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8523,11 +8549,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Kalkglänta 25 x 25 m.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8539,7 +8560,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8556,16 +8577,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771335</t>
+          <t>https://artportalen.se/Sighting/136771225</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136065783</v>
+        <v>136771312</v>
       </c>
       <c r="B71" t="n">
-        <v>107305</v>
+        <v>110341</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8573,16 +8594,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8593,17 +8614,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>721065</v>
+        <v>721264</v>
       </c>
       <c r="R71" t="n">
-        <v>6379250</v>
+        <v>6379267</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8627,12 +8648,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8646,7 +8667,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8663,33 +8684,33 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065783</t>
+          <t>https://artportalen.se/Sighting/136771312</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136065789</v>
+        <v>136065769</v>
       </c>
       <c r="B72" t="n">
-        <v>107305</v>
+        <v>107057</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221903</v>
+        <v>220785</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8704,10 +8725,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>721062</v>
+        <v>721107</v>
       </c>
       <c r="R72" t="n">
-        <v>6379242</v>
+        <v>6379284</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8753,7 +8774,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
+          <t>Kalkbarrskog, gles.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8770,33 +8791,33 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065789</t>
+          <t>https://artportalen.se/Sighting/136065769</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136771207</v>
+        <v>136771252</v>
       </c>
       <c r="B73" t="n">
-        <v>107320</v>
+        <v>107072</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221903</v>
+        <v>220785</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8804,17 +8825,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>721228</v>
+        <v>721181</v>
       </c>
       <c r="R73" t="n">
-        <v>6379313</v>
+        <v>6379245</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8849,6 +8879,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Högre träd.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8860,7 +8895,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8877,33 +8912,33 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771207</t>
+          <t>https://artportalen.se/Sighting/136771252</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136771333</v>
+        <v>136771267</v>
       </c>
       <c r="B74" t="n">
-        <v>107320</v>
+        <v>107072</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221903</v>
+        <v>220785</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8918,13 +8953,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>721383</v>
+        <v>721235</v>
       </c>
       <c r="R74" t="n">
-        <v>6379285</v>
+        <v>6379245</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8956,11 +8991,6 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Kalkglänta 25 x 25 m.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8972,7 +9002,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Kalkglänta.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8989,33 +9019,33 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771333</t>
+          <t>https://artportalen.se/Sighting/136771267</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136065754</v>
+        <v>136771291</v>
       </c>
       <c r="B75" t="n">
-        <v>100400</v>
+        <v>107072</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222662</v>
+        <v>220785</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9023,20 +9053,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>721106</v>
+        <v>721235</v>
       </c>
       <c r="R75" t="n">
-        <v>6379184</v>
+        <v>6379263</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9060,12 +9099,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Litet träd.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9079,7 +9123,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Källmyrslik våtmark med gott om orkidéer.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9096,33 +9140,33 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065754</t>
+          <t>https://artportalen.se/Sighting/136771291</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136065761</v>
+        <v>136771295</v>
       </c>
       <c r="B76" t="n">
-        <v>99152</v>
+        <v>107072</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223049</v>
+        <v>220785</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9133,14 +9177,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>721144</v>
+        <v>721250</v>
       </c>
       <c r="R76" t="n">
-        <v>6379285</v>
+        <v>6379289</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9167,12 +9211,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Småplantor.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9186,7 +9235,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
+          <t>Kalkbarrskog, frisk, med gott om död ved. Träden delvis på socklar.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9203,33 +9252,33 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136065761</t>
+          <t>https://artportalen.se/Sighting/136771295</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136771308</v>
+        <v>136065753</v>
       </c>
       <c r="B77" t="n">
-        <v>99167</v>
+        <v>106383</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223049</v>
+        <v>221137</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9240,17 +9289,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>721264</v>
+        <v>721106</v>
       </c>
       <c r="R77" t="n">
-        <v>6379267</v>
+        <v>6379184</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9274,12 +9323,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9293,7 +9342,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9310,60 +9359,51 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771308</t>
+          <t>https://artportalen.se/Sighting/136065753</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136771210</v>
+        <v>136065785</v>
       </c>
       <c r="B78" t="n">
-        <v>99279</v>
+        <v>107764</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>223591</v>
+        <v>221849</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>721219</v>
+        <v>721065</v>
       </c>
       <c r="R78" t="n">
-        <v>6379304</v>
+        <v>6379250</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9390,12 +9430,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9409,7 +9449,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9426,60 +9466,51 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771210</t>
+          <t>https://artportalen.se/Sighting/136065785</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136771216</v>
+        <v>136065790</v>
       </c>
       <c r="B79" t="n">
-        <v>99279</v>
+        <v>107764</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>223591</v>
+        <v>221849</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>721218</v>
+        <v>721062</v>
       </c>
       <c r="R79" t="n">
-        <v>6379288</v>
+        <v>6379242</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9506,12 +9537,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9525,7 +9556,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9542,60 +9573,51 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771216</t>
+          <t>https://artportalen.se/Sighting/136065790</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136771228</v>
+        <v>136771275</v>
       </c>
       <c r="B80" t="n">
-        <v>99279</v>
+        <v>107779</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>223591</v>
+        <v>221849</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda, Broe 1:10 (3);., Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>721192</v>
+        <v>721257</v>
       </c>
       <c r="R80" t="n">
-        <v>6379281</v>
+        <v>6379214</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9641,7 +9663,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9658,63 +9680,54 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771228</t>
+          <t>https://artportalen.se/Sighting/136771275</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136771245</v>
+        <v>136771335</v>
       </c>
       <c r="B81" t="n">
-        <v>99279</v>
+        <v>107779</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>223591</v>
+        <v>221849</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>721173</v>
+        <v>721383</v>
       </c>
       <c r="R81" t="n">
-        <v>6379274</v>
+        <v>6379285</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9746,6 +9759,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Kalkglänta 25 x 25 m.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9757,7 +9775,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9774,60 +9792,51 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771245</t>
+          <t>https://artportalen.se/Sighting/136771335</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136771249</v>
+        <v>136065783</v>
       </c>
       <c r="B82" t="n">
-        <v>99279</v>
+        <v>107305</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>223591</v>
+        <v>221903</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>721177</v>
+        <v>721065</v>
       </c>
       <c r="R82" t="n">
-        <v>6379254</v>
+        <v>6379250</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9854,17 +9863,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Dike NV.</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9878,7 +9882,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9895,60 +9899,51 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771249</t>
+          <t>https://artportalen.se/Sighting/136065783</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136771257</v>
+        <v>136065789</v>
       </c>
       <c r="B83" t="n">
-        <v>99279</v>
+        <v>107305</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>221903</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>721191</v>
+        <v>721062</v>
       </c>
       <c r="R83" t="n">
-        <v>6379260</v>
+        <v>6379242</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9975,17 +9970,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Dike NV.</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9999,7 +9989,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog, gles med något kalk i dagen.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10016,60 +10006,51 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771257</t>
+          <t>https://artportalen.se/Sighting/136065789</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136771270</v>
+        <v>136771207</v>
       </c>
       <c r="B84" t="n">
-        <v>99279</v>
+        <v>107320</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>223591</v>
+        <v>221903</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>721235</v>
+        <v>721228</v>
       </c>
       <c r="R84" t="n">
-        <v>6379245</v>
+        <v>6379313</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10115,7 +10096,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10132,63 +10113,54 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771270</t>
+          <t>https://artportalen.se/Sighting/136771207</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136771280</v>
+        <v>136771333</v>
       </c>
       <c r="B85" t="n">
-        <v>99279</v>
+        <v>107320</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>223591</v>
+        <v>221903</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>721243</v>
+        <v>721383</v>
       </c>
       <c r="R85" t="n">
-        <v>6379246</v>
+        <v>6379285</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10220,6 +10192,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Kalkglänta 25 x 25 m.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10231,7 +10208,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+          <t>Kalkglänta.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10248,16 +10225,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771280</t>
+          <t>https://artportalen.se/Sighting/136771333</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136771353</v>
+        <v>136065754</v>
       </c>
       <c r="B86" t="n">
-        <v>99279</v>
+        <v>100400</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10265,46 +10242,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>223591</v>
+        <v>222662</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>721295</v>
+        <v>721106</v>
       </c>
       <c r="R86" t="n">
-        <v>6379310</v>
+        <v>6379184</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10328,12 +10296,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10347,7 +10315,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Blandskog frisk nära dike.</t>
+          <t>Källmyrslik våtmark med gott om orkidéer.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10364,16 +10332,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136771353</t>
+          <t>https://artportalen.se/Sighting/136065754</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136771227</v>
+        <v>136065761</v>
       </c>
       <c r="B87" t="n">
-        <v>106489</v>
+        <v>99152</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10381,43 +10349,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>224098</v>
+        <v>223049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Wallr.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+          <t>Norrlanda Broe 1:10 (3) A 33289-2026., Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>721197</v>
+        <v>721144</v>
       </c>
       <c r="R87" t="n">
-        <v>6379286</v>
+        <v>6379285</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10444,12 +10403,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10463,7 +10422,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+          <t>Kalkbarrskog, tätare skog med större graninslag.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10480,7 +10439,1740 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136065761</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>136771308</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99167</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>721264</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6379267</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771308</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>136771210</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>721219</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6379304</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771210</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>136771216</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>721218</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6379288</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771216</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>136771228</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>721192</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6379281</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771228</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>136771245</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>721173</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6379274</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771245</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>136771249</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>721177</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6379254</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, på högre liggande kullar i våtmark.</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771249</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>136771257</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>721191</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6379260</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Dike NV.</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771257</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>136771270</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>721235</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6379245</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771270</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>136771280</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>721243</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6379246</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, frisk, med gott om död ved.</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771280</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>136771353</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99279</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>721295</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6379310</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Blandskog frisk nära dike.</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136771353</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>136771227</v>
+      </c>
+      <c r="B98" t="n">
+        <v>106489</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>721197</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6379286</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Fuktmark i skog, tuvig med jordblottor.</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136771227</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>137090315</v>
+      </c>
+      <c r="B99" t="n">
+        <v>87444</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>A 33289-2026 Norrlanda Broe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>721245</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6379303</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137090315</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>137090257</v>
+      </c>
+      <c r="B100" t="n">
+        <v>87528</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>721214</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6379294</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137090257</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>137090262</v>
+      </c>
+      <c r="B101" t="n">
+        <v>87528</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Norrlanda Broe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>721117</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6379233</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137090262</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>137090318</v>
+      </c>
+      <c r="B102" t="n">
+        <v>87528</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>A 33289-2026 Norrlanda Broe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>721265</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6379312</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137090318</t>
         </is>
       </c>
     </row>
@@ -10572,6 +12264,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -2294,7 +2294,7 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 33289-2026 Norrlanda Broe, Gtl</t>
+          <t>Norrlanda Broe, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100592</v>
+        <v>100598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100592</v>
+        <v>100598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100592</v>
+        <v>100598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100592</v>
+        <v>100598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87416</v>
+        <v>87422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87416</v>
+        <v>87422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91551</v>
+        <v>91557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87595</v>
+        <v>87601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111660</v>
+        <v>111666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99385</v>
+        <v>99391</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99385</v>
+        <v>99391</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108379</v>
+        <v>108385</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108379</v>
+        <v>108385</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108379</v>
+        <v>108385</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108379</v>
+        <v>108385</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104897</v>
+        <v>104903</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104897</v>
+        <v>104903</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110342</v>
+        <v>110348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110342</v>
+        <v>110348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107780</v>
+        <v>107786</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107780</v>
+        <v>107786</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107321</v>
+        <v>107327</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107321</v>
+        <v>107327</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99168</v>
+        <v>99174</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99280</v>
+        <v>99286</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106490</v>
+        <v>106496</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89266</v>
+        <v>89272</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87552</v>
+        <v>87558</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87445</v>
+        <v>87451</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100598</v>
+        <v>100602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100598</v>
+        <v>100602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100598</v>
+        <v>100602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100598</v>
+        <v>100602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87422</v>
+        <v>87426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87422</v>
+        <v>87426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87601</v>
+        <v>87605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>721215</v>
       </c>
       <c r="R16" t="n">
-        <v>6379263</v>
+        <v>6379262</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99391</v>
+        <v>99395</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99391</v>
+        <v>99395</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108385</v>
+        <v>108389</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108385</v>
+        <v>108389</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108385</v>
+        <v>108389</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108385</v>
+        <v>108389</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104903</v>
+        <v>104907</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104903</v>
+        <v>104907</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110348</v>
+        <v>110352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110348</v>
+        <v>110352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107786</v>
+        <v>107790</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107786</v>
+        <v>107790</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107327</v>
+        <v>107331</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107327</v>
+        <v>107331</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99174</v>
+        <v>99178</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99286</v>
+        <v>99290</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106496</v>
+        <v>106500</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89272</v>
+        <v>89276</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87558</v>
+        <v>87562</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87451</v>
+        <v>87455</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -2301,7 +2301,7 @@
         <v>721215</v>
       </c>
       <c r="R16" t="n">
-        <v>6379262</v>
+        <v>6379263</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100602</v>
+        <v>100604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100602</v>
+        <v>100604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100602</v>
+        <v>100604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100602</v>
+        <v>100604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99395</v>
+        <v>99397</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99395</v>
+        <v>99397</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108389</v>
+        <v>108391</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108389</v>
+        <v>108391</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108389</v>
+        <v>108391</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108389</v>
+        <v>108391</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104907</v>
+        <v>104909</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104907</v>
+        <v>104909</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110352</v>
+        <v>110354</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110352</v>
+        <v>110354</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107790</v>
+        <v>107792</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107790</v>
+        <v>107792</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99290</v>
+        <v>99292</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100604</v>
+        <v>100606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100604</v>
+        <v>100606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100604</v>
+        <v>100606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100604</v>
+        <v>100606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87426</v>
+        <v>87428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87426</v>
+        <v>87428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87605</v>
+        <v>87607</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>721215</v>
       </c>
       <c r="R16" t="n">
-        <v>6379263</v>
+        <v>6379262</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108391</v>
+        <v>108393</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108391</v>
+        <v>108393</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108391</v>
+        <v>108393</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108391</v>
+        <v>108393</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104909</v>
+        <v>104911</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104909</v>
+        <v>104911</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110354</v>
+        <v>110356</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110354</v>
+        <v>110356</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107792</v>
+        <v>107794</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107792</v>
+        <v>107794</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106502</v>
+        <v>106504</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89276</v>
+        <v>89278</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87562</v>
+        <v>87564</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100606</v>
+        <v>100619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100606</v>
+        <v>100619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100606</v>
+        <v>100619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100606</v>
+        <v>100619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87428</v>
+        <v>87441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87428</v>
+        <v>87441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87607</v>
+        <v>87620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>721215</v>
       </c>
       <c r="R16" t="n">
-        <v>6379262</v>
+        <v>6379263</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136774891</v>
       </c>
       <c r="B31" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136774892</v>
       </c>
       <c r="B32" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>136774893</v>
       </c>
       <c r="B33" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>136774894</v>
       </c>
       <c r="B34" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>136774895</v>
       </c>
       <c r="B35" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>136774896</v>
       </c>
       <c r="B36" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>136774897</v>
       </c>
       <c r="B37" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136774898</v>
       </c>
       <c r="B38" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136774899</v>
       </c>
       <c r="B39" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108393</v>
+        <v>108406</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108393</v>
+        <v>108406</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108393</v>
+        <v>108406</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108393</v>
+        <v>108406</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104911</v>
+        <v>104924</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104911</v>
+        <v>104924</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110356</v>
+        <v>110369</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110356</v>
+        <v>110369</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107794</v>
+        <v>107807</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107794</v>
+        <v>107807</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107335</v>
+        <v>107348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107335</v>
+        <v>107348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99182</v>
+        <v>99195</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99294</v>
+        <v>99307</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106504</v>
+        <v>106517</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89278</v>
+        <v>89291</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100619</v>
+        <v>100621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100619</v>
+        <v>100621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100619</v>
+        <v>100621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100619</v>
+        <v>100621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87441</v>
+        <v>87443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87441</v>
+        <v>87443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87620</v>
+        <v>87622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>721215</v>
       </c>
       <c r="R16" t="n">
-        <v>6379263</v>
+        <v>6379262</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136774891</v>
       </c>
       <c r="B31" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>136774892</v>
       </c>
       <c r="B32" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>136774893</v>
       </c>
       <c r="B33" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>136774894</v>
       </c>
       <c r="B34" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>136774895</v>
       </c>
       <c r="B35" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>136774896</v>
       </c>
       <c r="B36" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>136774897</v>
       </c>
       <c r="B37" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>136774898</v>
       </c>
       <c r="B38" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>136774899</v>
       </c>
       <c r="B39" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108406</v>
+        <v>108408</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108406</v>
+        <v>108408</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108406</v>
+        <v>108408</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108406</v>
+        <v>108408</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104924</v>
+        <v>104926</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104924</v>
+        <v>104926</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110369</v>
+        <v>110371</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110369</v>
+        <v>110371</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107807</v>
+        <v>107809</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107807</v>
+        <v>107809</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107348</v>
+        <v>107350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107348</v>
+        <v>107350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99195</v>
+        <v>99197</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99307</v>
+        <v>99309</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106517</v>
+        <v>106519</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89291</v>
+        <v>89293</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -4007,11 +4007,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -4124,11 +4120,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -4241,11 +4233,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -4358,11 +4346,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -4475,11 +4459,7 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -4592,11 +4572,7 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -4709,11 +4685,7 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -4826,11 +4798,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -4943,11 +4911,7 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -7150,11 +7114,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>
@@ -7722,11 +7682,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Norrlanda, Broe 1:10 (3); AVA: A 33289-2026., Gtl</t>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100621</v>
+        <v>100624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100621</v>
+        <v>100624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100621</v>
+        <v>100624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100621</v>
+        <v>100624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87443</v>
+        <v>87446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87443</v>
+        <v>87446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87622</v>
+        <v>87625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108408</v>
+        <v>108413</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108408</v>
+        <v>108413</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108408</v>
+        <v>108413</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108408</v>
+        <v>108413</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104926</v>
+        <v>104929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104926</v>
+        <v>104929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110371</v>
+        <v>110376</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110371</v>
+        <v>110376</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107809</v>
+        <v>107813</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107809</v>
+        <v>107813</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107350</v>
+        <v>107354</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107350</v>
+        <v>107354</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99197</v>
+        <v>99200</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99309</v>
+        <v>99312</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99309</v>
+        <v>99312</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99309</v>
+        <v>99312</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99309</v>
+        <v>99312</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99309</v>
+        <v>99312</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99309</v>
+        <v>99312</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99309</v>
+        <v>99312</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99309</v>
+        <v>99312</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99309</v>
+        <v>99312</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106519</v>
+        <v>106523</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89293</v>
+        <v>89296</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100624</v>
+        <v>100634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100624</v>
+        <v>100634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100624</v>
+        <v>100634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100624</v>
+        <v>100634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87446</v>
+        <v>87456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87446</v>
+        <v>87456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87625</v>
+        <v>87635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>721215</v>
       </c>
       <c r="R16" t="n">
-        <v>6379262</v>
+        <v>6379263</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136774891</v>
       </c>
       <c r="B31" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136774892</v>
       </c>
       <c r="B32" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>136774893</v>
       </c>
       <c r="B33" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>136774894</v>
       </c>
       <c r="B34" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>136774895</v>
       </c>
       <c r="B35" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136774896</v>
       </c>
       <c r="B36" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>136774897</v>
       </c>
       <c r="B37" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>136774898</v>
       </c>
       <c r="B38" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>136774899</v>
       </c>
       <c r="B39" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108413</v>
+        <v>108434</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108413</v>
+        <v>108434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108413</v>
+        <v>108434</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108413</v>
+        <v>108434</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104929</v>
+        <v>104948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104929</v>
+        <v>104948</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110376</v>
+        <v>110398</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110376</v>
+        <v>110398</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107813</v>
+        <v>107834</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107813</v>
+        <v>107834</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107354</v>
+        <v>107374</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107354</v>
+        <v>107374</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99200</v>
+        <v>99210</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99312</v>
+        <v>99322</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99312</v>
+        <v>99322</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99312</v>
+        <v>99322</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99312</v>
+        <v>99322</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99312</v>
+        <v>99322</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99312</v>
+        <v>99322</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99312</v>
+        <v>99322</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99312</v>
+        <v>99322</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99312</v>
+        <v>99322</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106523</v>
+        <v>106543</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89296</v>
+        <v>89306</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100634</v>
+        <v>100635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100634</v>
+        <v>100635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100634</v>
+        <v>100635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100634</v>
+        <v>100635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87456</v>
+        <v>87457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87456</v>
+        <v>87457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87635</v>
+        <v>87636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>721215</v>
       </c>
       <c r="R16" t="n">
-        <v>6379263</v>
+        <v>6379262</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108434</v>
+        <v>108435</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108434</v>
+        <v>108435</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108434</v>
+        <v>108435</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108434</v>
+        <v>108435</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104948</v>
+        <v>104949</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104948</v>
+        <v>104949</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107374</v>
+        <v>107375</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107374</v>
+        <v>107375</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99322</v>
+        <v>99323</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106543</v>
+        <v>106544</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89306</v>
+        <v>89307</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100635</v>
+        <v>100640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100635</v>
+        <v>100640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100635</v>
+        <v>100640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100635</v>
+        <v>100640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87636</v>
+        <v>87639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136774891</v>
       </c>
       <c r="B31" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136774892</v>
       </c>
       <c r="B32" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>136774893</v>
       </c>
       <c r="B33" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>136774894</v>
       </c>
       <c r="B34" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>136774895</v>
       </c>
       <c r="B35" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136774896</v>
       </c>
       <c r="B36" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>136774897</v>
       </c>
       <c r="B37" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>136774898</v>
       </c>
       <c r="B38" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>136774899</v>
       </c>
       <c r="B39" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108435</v>
+        <v>108440</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108435</v>
+        <v>108440</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108435</v>
+        <v>108440</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108435</v>
+        <v>108440</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104949</v>
+        <v>104954</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104949</v>
+        <v>104954</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107375</v>
+        <v>107380</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107375</v>
+        <v>107380</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99211</v>
+        <v>99216</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106544</v>
+        <v>106549</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89307</v>
+        <v>89310</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136771239</v>
       </c>
       <c r="B2" t="n">
-        <v>100640</v>
+        <v>100643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136771244</v>
       </c>
       <c r="B3" t="n">
-        <v>100640</v>
+        <v>100643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136771247</v>
       </c>
       <c r="B4" t="n">
-        <v>100640</v>
+        <v>100643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136771251</v>
       </c>
       <c r="B5" t="n">
-        <v>100640</v>
+        <v>100643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>136771236</v>
       </c>
       <c r="B40" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>136771218</v>
       </c>
       <c r="B44" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>136771219</v>
       </c>
       <c r="B45" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>136771250</v>
       </c>
       <c r="B46" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>136771253</v>
       </c>
       <c r="B47" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>136771259</v>
       </c>
       <c r="B48" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>136771261</v>
       </c>
       <c r="B49" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>136771265</v>
       </c>
       <c r="B50" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>136771271</v>
       </c>
       <c r="B51" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>136771272</v>
       </c>
       <c r="B52" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136771281</v>
       </c>
       <c r="B53" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>136771284</v>
       </c>
       <c r="B54" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>136771286</v>
       </c>
       <c r="B55" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>136771292</v>
       </c>
       <c r="B56" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>136771293</v>
       </c>
       <c r="B57" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>136771296</v>
       </c>
       <c r="B58" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>136771297</v>
       </c>
       <c r="B59" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>136771302</v>
       </c>
       <c r="B60" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>136771234</v>
       </c>
       <c r="B63" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>136771319</v>
       </c>
       <c r="B69" t="n">
-        <v>108440</v>
+        <v>108443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>136771320</v>
       </c>
       <c r="B70" t="n">
-        <v>108440</v>
+        <v>108443</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>136771321</v>
       </c>
       <c r="B71" t="n">
-        <v>108440</v>
+        <v>108443</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>136771340</v>
       </c>
       <c r="B72" t="n">
-        <v>108440</v>
+        <v>108443</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>136771276</v>
       </c>
       <c r="B76" t="n">
-        <v>104954</v>
+        <v>104957</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>136771336</v>
       </c>
       <c r="B77" t="n">
-        <v>104954</v>
+        <v>104957</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>136771225</v>
       </c>
       <c r="B79" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>136771312</v>
       </c>
       <c r="B80" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>136771252</v>
       </c>
       <c r="B82" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>136771267</v>
       </c>
       <c r="B83" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>136771291</v>
       </c>
       <c r="B84" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>136771295</v>
       </c>
       <c r="B85" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>136771275</v>
       </c>
       <c r="B89" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>136771335</v>
       </c>
       <c r="B90" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>136771207</v>
       </c>
       <c r="B93" t="n">
-        <v>107380</v>
+        <v>107383</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>136771333</v>
       </c>
       <c r="B94" t="n">
-        <v>107380</v>
+        <v>107383</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>136771308</v>
       </c>
       <c r="B97" t="n">
-        <v>99216</v>
+        <v>99218</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>136771210</v>
       </c>
       <c r="B98" t="n">
-        <v>99328</v>
+        <v>99330</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>136771216</v>
       </c>
       <c r="B99" t="n">
-        <v>99328</v>
+        <v>99330</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>136771228</v>
       </c>
       <c r="B100" t="n">
-        <v>99328</v>
+        <v>99330</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>136771245</v>
       </c>
       <c r="B101" t="n">
-        <v>99328</v>
+        <v>99330</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>136771249</v>
       </c>
       <c r="B102" t="n">
-        <v>99328</v>
+        <v>99330</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>136771257</v>
       </c>
       <c r="B103" t="n">
-        <v>99328</v>
+        <v>99330</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>136771270</v>
       </c>
       <c r="B104" t="n">
-        <v>99328</v>
+        <v>99330</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>136771280</v>
       </c>
       <c r="B105" t="n">
-        <v>99328</v>
+        <v>99330</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136771353</v>
       </c>
       <c r="B106" t="n">
-        <v>99328</v>
+        <v>99330</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>136771227</v>
       </c>
       <c r="B107" t="n">
-        <v>106549</v>
+        <v>106552</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87460</v>
+        <v>87465</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87460</v>
+        <v>87465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87639</v>
+        <v>87644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89310</v>
+        <v>89315</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -2301,7 +2301,7 @@
         <v>721215</v>
       </c>
       <c r="R16" t="n">
-        <v>6379263</v>
+        <v>6379262</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87465</v>
+        <v>87476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87465</v>
+        <v>87476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87644</v>
+        <v>87655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89315</v>
+        <v>89326</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87476</v>
+        <v>87477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87476</v>
+        <v>87477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87655</v>
+        <v>87656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89326</v>
+        <v>89327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87477</v>
+        <v>87480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87477</v>
+        <v>87480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87656</v>
+        <v>87659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89327</v>
+        <v>89330</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 33289-2026 artfynd.xlsx
+++ b/artfynd/A 33289-2026 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>137090260</v>
       </c>
       <c r="B6" t="n">
-        <v>87480</v>
+        <v>87484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137106608</v>
       </c>
       <c r="B7" t="n">
-        <v>87480</v>
+        <v>87484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>137105795</v>
       </c>
       <c r="B8" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137090253</v>
       </c>
       <c r="B9" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137090256</v>
       </c>
       <c r="B10" t="n">
-        <v>87659</v>
+        <v>87663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137090255</v>
       </c>
       <c r="B11" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>137090258</v>
       </c>
       <c r="B12" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137090259</v>
       </c>
       <c r="B13" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>137090261</v>
       </c>
       <c r="B14" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>137090263</v>
       </c>
       <c r="B15" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>137090314</v>
       </c>
       <c r="B16" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>721215</v>
       </c>
       <c r="R16" t="n">
-        <v>6379262</v>
+        <v>6379263</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2379,7 +2379,7 @@
         <v>137105791</v>
       </c>
       <c r="B17" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>137105792</v>
       </c>
       <c r="B18" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137090316</v>
       </c>
       <c r="B19" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137105787</v>
       </c>
       <c r="B20" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>137106609</v>
       </c>
       <c r="B21" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>137105794</v>
       </c>
       <c r="B22" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>137105786</v>
       </c>
       <c r="B23" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>137105788</v>
       </c>
       <c r="B24" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>137090254</v>
       </c>
       <c r="B64" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>137105784</v>
       </c>
       <c r="B108" t="n">
-        <v>89330</v>
+        <v>89334</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>137106610</v>
       </c>
       <c r="B109" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>137090315</v>
       </c>
       <c r="B110" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>137105789</v>
       </c>
       <c r="B111" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>137090257</v>
       </c>
       <c r="B112" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>137090262</v>
       </c>
       <c r="B113" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>137090318</v>
       </c>
       <c r="B114" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>137105785</v>
       </c>
       <c r="B115" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>137105790</v>
       </c>
       <c r="B116" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>137105793</v>
       </c>
       <c r="B117" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>137106607</v>
       </c>
       <c r="B118" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
